--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487631_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487631_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4878</v>
+        <v>4.7331</v>
       </c>
       <c r="E2" t="n">
         <v>2.2783</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2096</v>
+        <v>2.4548</v>
       </c>
       <c r="G2" t="n">
         <v>2.5259</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0664</v>
+        <v>0.1789</v>
       </c>
       <c r="T2" t="n">
         <v>-0.12</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0536</v>
+        <v>0.2989</v>
       </c>
       <c r="V2" t="n">
         <v>0.2821</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. BATLLE BERNARDO</t>
+          <t>M. ALARCON ORTIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1453</v>
+        <v>4.4976</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7122</v>
+        <v>1.7937</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4332</v>
+        <v>2.7039</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7339</v>
+        <v>3.1557</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2119</v>
+        <v>0.29</v>
       </c>
       <c r="I3" t="n">
-        <v>2.522</v>
+        <v>2.8657</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1853</v>
+        <v>2.0293</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3306</v>
+        <v>0.6262</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8547</v>
+        <v>1.4031</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5487</v>
+        <v>1.1264</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1187</v>
+        <v>-0.3362</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6673</v>
+        <v>1.4626</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3517</v>
+        <v>-0.464</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2434</v>
+        <v>-0.7714</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1084</v>
+        <v>0.3073</v>
       </c>
       <c r="V3" t="n">
         <v>1.2239</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ALARCON ORTIZ</t>
+          <t>M. BATLLE BERNARDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8336</v>
+        <v>4.0631</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2932</v>
+        <v>2.4119</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5404</v>
+        <v>1.6512</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1557</v>
+        <v>3.7339</v>
       </c>
       <c r="H4" t="n">
-        <v>0.29</v>
+        <v>1.2119</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8657</v>
+        <v>2.522</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0293</v>
+        <v>3.1853</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6262</v>
+        <v>1.3306</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4031</v>
+        <v>1.8547</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1264</v>
+        <v>0.5487</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3362</v>
+        <v>-0.1187</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4626</v>
+        <v>0.6673</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5821</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1281</v>
+        <v>0.2695</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2719</v>
+        <v>-0.0569</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1438</v>
+        <v>0.3264</v>
       </c>
       <c r="V4" t="n">
         <v>1.2239</v>
       </c>
       <c r="W4" t="n">
-        <v>1.506</v>
+        <v>1.2239</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6397</v>
+        <v>3.0763</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5949</v>
+        <v>0.8952</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0448</v>
+        <v>2.1811</v>
       </c>
       <c r="G5" t="n">
         <v>2.7552</v>
@@ -844,13 +844,13 @@
         <v>0.5821</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6976</v>
+        <v>-0.261</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7268</v>
+        <v>-0.4265</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0292</v>
+        <v>0.1655</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1372</v>
+        <v>1.9648</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0361</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1733</v>
+        <v>2.9008</v>
       </c>
       <c r="G6" t="n">
         <v>2.5164</v>
@@ -922,13 +922,13 @@
         <v>2.1344</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7268</v>
+        <v>0.5543</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3623</v>
+        <v>-0.2622</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0891</v>
+        <v>0.8165</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3299</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8086</v>
+        <v>1.0544</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6656</v>
+        <v>0.5655</v>
       </c>
       <c r="F7" t="n">
-        <v>1.143</v>
+        <v>0.4889</v>
       </c>
       <c r="G7" t="n">
         <v>2.1475</v>
@@ -1000,13 +1000,13 @@
         <v>0.9702</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1386</v>
+        <v>0.3844</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4834</v>
+        <v>-0.5835</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6221</v>
+        <v>0.968</v>
       </c>
       <c r="V7" t="n">
         <v>-2.4477</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SANZ CÁMARA</t>
+          <t>G. PACHECO TABERNERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8032</v>
+        <v>0.321</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0546</v>
+        <v>-0.04</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8577</v>
+        <v>0.361</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6627</v>
+        <v>0.215</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2722</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6095</v>
+        <v>0.1335</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3683</v>
+        <v>0.0206</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6395</v>
+        <v>0.0206</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2712</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2945</v>
+        <v>0.1944</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6327</v>
+        <v>0.061</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.1335</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5523</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0061</v>
+        <v>0.106</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5473</v>
+        <v>-0.0606</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4588</v>
+        <v>0.1666</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. PACHECO TABERNERO</t>
+          <t>M. SANZ CÁMARA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4028</v>
+        <v>0.2303</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04</v>
+        <v>-0.3549</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4428</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.215</v>
+        <v>1.6627</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08160000000000001</v>
+        <v>2.2722</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1335</v>
+        <v>-0.6095</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0206</v>
+        <v>0.3683</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0206</v>
+        <v>1.6395</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.2712</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1944</v>
+        <v>1.2945</v>
       </c>
       <c r="N9" t="n">
-        <v>0.061</v>
+        <v>0.6327</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1335</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5821</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5523</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1878</v>
+        <v>0.4332</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0606</v>
+        <v>0.247</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2483</v>
+        <v>0.1862</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>F. SANTAMARIA LEON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0514</v>
+        <v>-0.0215</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9325</v>
+        <v>-0.5646</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9838</v>
+        <v>0.5431</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7299</v>
+        <v>-0.1216</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1303</v>
+        <v>-0.2373</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4004</v>
+        <v>0.1157</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2523</v>
+        <v>0.0234</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2523</v>
+        <v>0.0412</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.0178</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5223</v>
+        <v>-0.145</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1219</v>
+        <v>-0.2785</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4004</v>
+        <v>0.1335</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7761</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R10" t="n">
-        <v>0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8428</v>
+        <v>0.2061</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4251</v>
+        <v>0.1001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4177</v>
+        <v>0.106</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6119</v>
+        <v>0.2821</v>
       </c>
       <c r="W10" t="n">
-        <v>2.7298</v>
+        <v>0.2821</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. SANTAMARIA LEON</t>
+          <t>J. TRUJILLO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1488</v>
+        <v>-0.2612</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6647</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5158</v>
+        <v>0.5508</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1216</v>
+        <v>0.1512</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2373</v>
+        <v>-0.3304</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1157</v>
+        <v>0.4816</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0234</v>
+        <v>-0.8209</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0412</v>
+        <v>-0.2348</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0178</v>
+        <v>-0.5861</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.145</v>
+        <v>0.9721</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2785</v>
+        <v>-0.0956</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1335</v>
+        <v>1.0677</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3881</v>
+        <v>-0.194</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.2184</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-0.2448</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0264</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2821</v>
+        <v>1.2239</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. TRUJILLO FERNÁNDEZ</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8613</v>
+        <v>-0.3334</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1123</v>
+        <v>0.7323</v>
       </c>
       <c r="F12" t="n">
-        <v>0.251</v>
+        <v>-1.0656</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1512</v>
+        <v>-0.7299</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3304</v>
+        <v>-1.1303</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4816</v>
+        <v>0.4004</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8209</v>
+        <v>-1.2523</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2348</v>
+        <v>-1.2523</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5861</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9721</v>
+        <v>0.5223</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0956</v>
+        <v>0.1219</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0677</v>
+        <v>0.4004</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.194</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8185</v>
+        <v>0.5608</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5451</v>
+        <v>0.2249</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2734</v>
+        <v>0.3359</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2239</v>
+        <v>2.7298</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2239</v>
+        <v>-2.1179</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8897</v>
+        <v>-3.0175</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7912</v>
+        <v>-5.1916</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9015</v>
+        <v>2.1741</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1936</v>
@@ -1468,13 +1468,13 @@
         <v>1.7463</v>
       </c>
       <c r="S13" t="n">
-        <v>0.498</v>
+        <v>0.3701</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1839</v>
+        <v>-0.2165</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3141</v>
+        <v>0.5866</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1504,7 +1504,7 @@
         <v>16.307</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7778000000000009</v>
+        <v>0.7777999999999983</v>
       </c>
       <c r="F14" t="n">
         <v>15.5293</v>
@@ -1528,7 +1528,7 @@
         <v>1.5575</v>
       </c>
       <c r="M14" t="n">
-        <v>7.0983</v>
+        <v>7.098300000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-2.8839</v>
@@ -1537,7 +1537,7 @@
         <v>9.9823</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9702999999999999</v>
+        <v>0.9702999999999995</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.6421</v>
@@ -1552,13 +1552,13 @@
         <v>-2.1704</v>
       </c>
       <c r="U14" t="n">
-        <v>4.290400000000001</v>
+        <v>4.2903</v>
       </c>
       <c r="V14" t="n">
         <v>-1.601400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>6.870200000000001</v>
+        <v>6.8702</v>
       </c>
       <c r="X14" t="n">
         <v>-8.471500000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8122</v>
+        <v>3.2676</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0959</v>
+        <v>3.3962</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7163</v>
+        <v>-0.1286</v>
       </c>
       <c r="G15" t="n">
         <v>0.7709</v>
@@ -1624,13 +1624,13 @@
         <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0115</v>
+        <v>0.4669</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6528</v>
+        <v>-0.3525</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6642</v>
+        <v>0.8193</v>
       </c>
       <c r="V15" t="n">
         <v>1.8358</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4847</v>
+        <v>2.2473</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2398</v>
+        <v>4.1387</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7551</v>
+        <v>-1.8914</v>
       </c>
       <c r="G16" t="n">
         <v>1.7946</v>
@@ -1702,13 +1702,13 @@
         <v>0.3881</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6319</v>
+        <v>0.3945</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2146</v>
+        <v>0.1135</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4172</v>
+        <v>0.281</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3299</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.229</v>
+        <v>-0.0891</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3431</v>
+        <v>-0.4432</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.354</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5413</v>
@@ -1780,13 +1780,13 @@
         <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4121</v>
+        <v>0.0939</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.12</v>
+        <v>-0.2201</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5321</v>
+        <v>0.3141</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6119</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8902</v>
+        <v>-0.9034</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4939</v>
+        <v>-0.2019</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6038</v>
+        <v>-0.7015</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.7262</v>
+        <v>-1.2921</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8298</v>
+        <v>-0.608</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8964</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.5004</v>
+        <v>0.0824</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4984</v>
+        <v>0.0824</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.002</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2258</v>
+        <v>-1.3744</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3314</v>
+        <v>-0.6904</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1056</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0002</v>
+        <v>-0.1935</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4711</v>
+        <v>-0.2843</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4713</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1582</v>
+        <v>-1.0993</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4021</v>
+        <v>-1.594</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.756</v>
+        <v>0.4947</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2921</v>
+        <v>-3.7262</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.608</v>
+        <v>-1.8298</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-1.8964</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0824</v>
+        <v>-2.5004</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0824</v>
+        <v>-0.4984</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-2.002</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3744</v>
+        <v>-1.2258</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6904</v>
+        <v>-1.3314</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.1056</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4482</v>
+        <v>-0.2089</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4845</v>
+        <v>-0.5712</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0363</v>
+        <v>0.3623</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3225</v>
+        <v>-2.6233</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.911</v>
+        <v>-3.5116</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5885</v>
+        <v>0.8883</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9386</v>
@@ -2014,13 +2014,13 @@
         <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1019</v>
+        <v>-0.4027</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1962</v>
+        <v>-0.4044</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2981</v>
+        <v>0.0017</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2821</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0745</v>
+        <v>-3.1924</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3601</v>
+        <v>-3.8596</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2857</v>
+        <v>0.6672</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8467</v>
@@ -2092,13 +2092,13 @@
         <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5278</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1508</v>
+        <v>-0.6503</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3771</v>
+        <v>0.0045</v>
       </c>
       <c r="V21" t="n">
         <v>-0.894</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6225</v>
+        <v>-4.2771</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.444</v>
+        <v>-3.3439</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1785</v>
+        <v>-0.9332</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1075</v>
@@ -2170,13 +2170,13 @@
         <v>0.7761</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0971</v>
+        <v>-0.7517</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8962</v>
+        <v>-0.7961</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.201</v>
+        <v>0.0443</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2239</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1972</v>
+        <v>-4.606</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1361</v>
+        <v>-3.7357</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0611</v>
+        <v>-0.8703</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4481</v>
@@ -2248,13 +2248,13 @@
         <v>1.1642</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.3236</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.775</v>
+        <v>-0.3746</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1397</v>
+        <v>0.051</v>
       </c>
       <c r="V23" t="n">
         <v>0.9418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5678</v>
+        <v>-5.0311</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.7745</v>
+        <v>-6.3741</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2067</v>
+        <v>1.3429</v>
       </c>
       <c r="G24" t="n">
         <v>-1.4836</v>
@@ -2326,13 +2326,13 @@
         <v>1.1642</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0857</v>
+        <v>-0.549</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1508</v>
+        <v>-0.7504</v>
       </c>
       <c r="U24" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.2014</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2821</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-16.307</v>
+        <v>-16.3068</v>
       </c>
       <c r="E25" t="n">
         <v>-15.5291</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7776000000000001</v>
+        <v>-0.7779</v>
       </c>
       <c r="G25" t="n">
         <v>-14.8186</v>
@@ -2404,13 +2404,13 @@
         <v>11.642</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.119800000000001</v>
+        <v>-2.1198</v>
       </c>
       <c r="T25" t="n">
         <v>-4.2904</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1703</v>
+        <v>2.1704</v>
       </c>
       <c r="V25" t="n">
         <v>1.6014</v>
